--- a/Template_HRC_olimpica.xlsx
+++ b/Template_HRC_olimpica.xlsx
@@ -467,9 +467,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:I75"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
@@ -487,6 +499,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -494,6 +507,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -544,6 +558,8 @@
         <v>-141739081.6399999</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -586,6 +602,11 @@
         <v>1047007047</v>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="7" t="inlineStr">
         <is>
